--- a/public/estochabitatge.xlsx
+++ b/public/estochabitatge.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99C0B306-D4AC-4AFF-932E-2B1CD9D1EC27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3933A021-7AAB-4795-9E42-90E434368052}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" tabRatio="496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,9 +33,6 @@
     <t>Catalunya</t>
   </si>
   <si>
-    <t>%</t>
-  </si>
-  <si>
     <t>Barcelona</t>
   </si>
   <si>
@@ -54,10 +51,13 @@
     <t>Venda</t>
   </si>
   <si>
-    <t>Llogar</t>
+    <t>Evolució des de 2021</t>
   </si>
   <si>
-    <t>Evolució des de 2021</t>
+    <t>Lloguer</t>
+  </si>
+  <si>
+    <t>% Enguany</t>
   </si>
 </sst>
 </file>
@@ -628,7 +628,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21.6328125" customWidth="1"/>
-    <col min="2" max="2" width="12.7265625" customWidth="1"/>
+    <col min="2" max="2" width="19.6328125" customWidth="1"/>
     <col min="3" max="3" width="14.36328125" customWidth="1"/>
     <col min="4" max="4" width="12.7265625" customWidth="1"/>
     <col min="5" max="5" width="15.453125" customWidth="1"/>
@@ -647,14 +647,14 @@
   <sheetData>
     <row r="1" spans="1:10" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C1" s="7">
         <f ca="1">TODAY()</f>
-        <v>46145</v>
+        <v>46299</v>
       </c>
       <c r="D1" s="7">
         <v>46023</v>
@@ -675,19 +675,19 @@
         <v>44197</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" s="3">
         <f>(C2*100/D2)-100</f>
-        <v>11.661618347035912</v>
+        <v>25.270445694504545</v>
       </c>
       <c r="C2" s="11">
-        <v>5161</v>
+        <v>5790</v>
       </c>
       <c r="D2" s="11">
         <v>4622</v>
@@ -709,19 +709,19 @@
       </c>
       <c r="J2" s="3">
         <f>(C2*100/I2)-100</f>
-        <v>-60.370114412961684</v>
+        <v>-55.540198111034321</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" s="3">
-        <f t="shared" ref="B3:B7" si="0">(C3*100/D3)-100</f>
-        <v>0.72271022823110798</v>
+        <f t="shared" ref="B3:B6" si="0">(C3*100/D3)-100</f>
+        <v>7.0558316357644202</v>
       </c>
       <c r="C3" s="11">
-        <v>77628</v>
+        <v>82509</v>
       </c>
       <c r="D3" s="11">
         <v>77071</v>
@@ -742,20 +742,20 @@
         <v>145180</v>
       </c>
       <c r="J3" s="3">
-        <f t="shared" ref="J3:J7" si="1">(C3*100/I3)-100</f>
-        <v>-46.529825044772004</v>
+        <f>(C3*100/I3)-100</f>
+        <v>-43.167791706846671</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4" s="3">
         <f t="shared" si="0"/>
-        <v>1.5231163229545785</v>
+        <v>7.3190456934896844</v>
       </c>
       <c r="C4" s="11">
-        <v>15064</v>
+        <v>15924</v>
       </c>
       <c r="D4" s="11">
         <v>14838</v>
@@ -776,8 +776,8 @@
         <v>23155</v>
       </c>
       <c r="J4" s="3">
-        <f t="shared" si="1"/>
-        <v>-34.942776938026341</v>
+        <f>(C4*100/I4)-100</f>
+        <v>-31.228676311811711</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -786,10 +786,10 @@
       </c>
       <c r="B5" s="3">
         <f t="shared" si="0"/>
-        <v>-2.6902173913043441</v>
+        <v>-2.8149703557312193</v>
       </c>
       <c r="C5" s="11">
-        <v>78782</v>
+        <v>78681</v>
       </c>
       <c r="D5" s="11">
         <v>80960</v>
@@ -810,20 +810,20 @@
         <v>117586</v>
       </c>
       <c r="J5" s="3">
-        <f t="shared" si="1"/>
-        <v>-33.000527273655024</v>
+        <f>(C5*100/I5)-100</f>
+        <v>-33.086421852941683</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="3">
         <f t="shared" si="0"/>
-        <v>11.503496503496507</v>
+        <v>10.8041958041958</v>
       </c>
       <c r="C6" s="11">
-        <v>3189</v>
+        <v>3169</v>
       </c>
       <c r="D6" s="11">
         <v>2860</v>
@@ -844,20 +844,20 @@
         <v>5954</v>
       </c>
       <c r="J6" s="3">
-        <f t="shared" si="1"/>
-        <v>-46.439368491770239</v>
+        <f>(C6*100/I6)-100</f>
+        <v>-46.7752771246221</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" s="3">
         <f>(C7*100/D7)-100</f>
-        <v>0.82822085889570474</v>
+        <v>-0.65293602103417925</v>
       </c>
       <c r="C7" s="11">
-        <v>23009</v>
+        <v>22671</v>
       </c>
       <c r="D7" s="11">
         <v>22820</v>
@@ -878,8 +878,8 @@
         <v>35814</v>
       </c>
       <c r="J7" s="3">
-        <f t="shared" si="1"/>
-        <v>-35.754174345228122</v>
+        <f>(C7*100/I7)-100</f>
+        <v>-36.697939353325516</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
@@ -892,11 +892,11 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C9" s="7">
         <f ca="1">TODAY()</f>
-        <v>46145</v>
+        <v>46299</v>
       </c>
       <c r="D9" s="7">
         <v>46023</v>
@@ -917,19 +917,19 @@
         <v>44197</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B10" s="3">
         <f>(C10*100/D10)-100</f>
-        <v>-1.0977337110481642</v>
+        <v>-12.110481586402273</v>
       </c>
       <c r="C10" s="11">
-        <v>2793</v>
+        <v>2482</v>
       </c>
       <c r="D10" s="11">
         <v>2824</v>
@@ -951,19 +951,19 @@
       </c>
       <c r="J10" s="3">
         <f>(C10*100/I10)-100</f>
-        <v>-54.152987524622453</v>
+        <v>-59.258043335521997</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B11" s="3">
-        <f t="shared" ref="B11:B15" si="2">(C11*100/D11)-100</f>
-        <v>-5.8013923341601981</v>
+        <f t="shared" ref="B11:B14" si="1">(C11*100/D11)-100</f>
+        <v>2.5286068656477596</v>
       </c>
       <c r="C11" s="11">
-        <v>11772</v>
+        <v>12813</v>
       </c>
       <c r="D11" s="11">
         <v>12497</v>
@@ -984,20 +984,20 @@
         <v>15873</v>
       </c>
       <c r="J11" s="3">
-        <f t="shared" ref="J11:J15" si="3">(C11*100/I11)-100</f>
-        <v>-25.836325836325841</v>
+        <f t="shared" ref="J11:J15" si="2">(C11*100/I11)-100</f>
+        <v>-19.278019278019272</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B12" s="3">
-        <f t="shared" si="2"/>
-        <v>-38.919036249186021</v>
+        <f t="shared" si="1"/>
+        <v>-44.58432819622314</v>
       </c>
       <c r="C12" s="11">
-        <v>2814</v>
+        <v>2553</v>
       </c>
       <c r="D12" s="11">
         <v>4607</v>
@@ -1018,8 +1018,8 @@
         <v>18442</v>
       </c>
       <c r="J12" s="3">
-        <f t="shared" si="3"/>
-        <v>-84.741351263420455</v>
+        <f t="shared" si="2"/>
+        <v>-86.156599067346278</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -1027,11 +1027,11 @@
         <v>0</v>
       </c>
       <c r="B13" s="3">
-        <f t="shared" si="2"/>
-        <v>-30.451175065979641</v>
+        <f t="shared" si="1"/>
+        <v>-32.424280507729037</v>
       </c>
       <c r="C13" s="11">
-        <v>5534</v>
+        <v>5377</v>
       </c>
       <c r="D13" s="11">
         <v>7957</v>
@@ -1052,20 +1052,20 @@
         <v>23713</v>
       </c>
       <c r="J13" s="3">
-        <f t="shared" si="3"/>
-        <v>-76.662590140429302</v>
+        <f t="shared" si="2"/>
+        <v>-77.324674229325694</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B14" s="3">
-        <f t="shared" si="2"/>
-        <v>-14.016489988221437</v>
+        <f t="shared" si="1"/>
+        <v>-10.482921083627801</v>
       </c>
       <c r="C14" s="11">
-        <v>730</v>
+        <v>760</v>
       </c>
       <c r="D14" s="11">
         <v>849</v>
@@ -1086,20 +1086,20 @@
         <v>2623</v>
       </c>
       <c r="J14" s="3">
-        <f t="shared" si="3"/>
-        <v>-72.169271826153263</v>
+        <f t="shared" si="2"/>
+        <v>-71.025543271063668</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B15" s="3">
         <f>(C15*100/D15)-100</f>
-        <v>-8.7180636485880711</v>
+        <v>0.24652622142536984</v>
       </c>
       <c r="C15" s="11">
-        <v>4073</v>
+        <v>4473</v>
       </c>
       <c r="D15" s="11">
         <v>4462</v>
@@ -1120,8 +1120,8 @@
         <v>7977</v>
       </c>
       <c r="J15" s="3">
-        <f t="shared" si="3"/>
-        <v>-48.940704525510846</v>
+        <f t="shared" si="2"/>
+        <v>-43.9262880782249</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
